--- a/artfynd/A 16644-2026 artfynd.xlsx
+++ b/artfynd/A 16644-2026 artfynd.xlsx
@@ -2105,32 +2105,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133211042</v>
+        <v>133211052</v>
       </c>
       <c r="B15" t="n">
-        <v>91918</v>
+        <v>91881</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2140,10 +2140,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>633917</v>
+        <v>633829</v>
       </c>
       <c r="R15" t="n">
-        <v>7001045</v>
+        <v>7000951</v>
       </c>
       <c r="S15" t="n">
         <v>3</v>
@@ -2175,7 +2175,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>17:24</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2185,7 +2185,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>17:24</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2212,32 +2212,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>133211052</v>
+        <v>133211042</v>
       </c>
       <c r="B16" t="n">
-        <v>91881</v>
+        <v>91918</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2247,10 +2247,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>633829</v>
+        <v>633917</v>
       </c>
       <c r="R16" t="n">
-        <v>7000951</v>
+        <v>7001045</v>
       </c>
       <c r="S16" t="n">
         <v>3</v>
@@ -2282,7 +2282,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>17:24</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2292,7 +2292,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>17:24</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AD16" t="b">

--- a/artfynd/A 16644-2026 artfynd.xlsx
+++ b/artfynd/A 16644-2026 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133208875</v>
+        <v>133208877</v>
       </c>
       <c r="B2" t="n">
-        <v>92217</v>
+        <v>91881</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>658</v>
+        <v>5447</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>633908</v>
+        <v>633915</v>
       </c>
       <c r="R2" t="n">
-        <v>7001035</v>
+        <v>7000976</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,32 +782,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133208877</v>
+        <v>133208875</v>
       </c>
       <c r="B3" t="n">
-        <v>91881</v>
+        <v>92217</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5447</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>633915</v>
+        <v>633908</v>
       </c>
       <c r="R3" t="n">
-        <v>7000976</v>
+        <v>7001035</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -2105,32 +2105,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133211052</v>
+        <v>133211042</v>
       </c>
       <c r="B15" t="n">
-        <v>91881</v>
+        <v>91918</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2140,10 +2140,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>633829</v>
+        <v>633917</v>
       </c>
       <c r="R15" t="n">
-        <v>7000951</v>
+        <v>7001045</v>
       </c>
       <c r="S15" t="n">
         <v>3</v>
@@ -2175,7 +2175,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>17:24</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2185,7 +2185,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>17:24</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2212,32 +2212,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>133211042</v>
+        <v>133211052</v>
       </c>
       <c r="B16" t="n">
-        <v>91918</v>
+        <v>91881</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2247,10 +2247,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>633917</v>
+        <v>633829</v>
       </c>
       <c r="R16" t="n">
-        <v>7001045</v>
+        <v>7000951</v>
       </c>
       <c r="S16" t="n">
         <v>3</v>
@@ -2282,7 +2282,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>17:24</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2292,7 +2292,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>17:24</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2760,10 +2760,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>133211034</v>
+        <v>133211035</v>
       </c>
       <c r="B21" t="n">
-        <v>91918</v>
+        <v>79333</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2771,21 +2771,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2795,10 +2795,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>633915</v>
+        <v>633904</v>
       </c>
       <c r="R21" t="n">
-        <v>7001088</v>
+        <v>7001077</v>
       </c>
       <c r="S21" t="n">
         <v>3</v>
@@ -2830,7 +2830,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2840,7 +2840,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2867,10 +2867,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>133211035</v>
+        <v>133211034</v>
       </c>
       <c r="B22" t="n">
-        <v>79333</v>
+        <v>91918</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2878,21 +2878,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2902,10 +2902,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>633904</v>
+        <v>633915</v>
       </c>
       <c r="R22" t="n">
-        <v>7001077</v>
+        <v>7001088</v>
       </c>
       <c r="S22" t="n">
         <v>3</v>
@@ -2937,7 +2937,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2947,7 +2947,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD22" t="b">

--- a/artfynd/A 16644-2026 artfynd.xlsx
+++ b/artfynd/A 16644-2026 artfynd.xlsx
@@ -996,7 +996,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133208871</v>
+        <v>133208876</v>
       </c>
       <c r="B5" t="n">
         <v>91918</v>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>633910</v>
+        <v>633874</v>
       </c>
       <c r="R5" t="n">
-        <v>7001064</v>
+        <v>7001016</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,7 +1103,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133208876</v>
+        <v>133208871</v>
       </c>
       <c r="B6" t="n">
         <v>91918</v>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>633874</v>
+        <v>633910</v>
       </c>
       <c r="R6" t="n">
-        <v>7001016</v>
+        <v>7001064</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1183,7 +1183,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 16644-2026 artfynd.xlsx
+++ b/artfynd/A 16644-2026 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133208877</v>
+        <v>133208875</v>
       </c>
       <c r="B2" t="n">
-        <v>91881</v>
+        <v>92217</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5447</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>633915</v>
+        <v>633908</v>
       </c>
       <c r="R2" t="n">
-        <v>7000976</v>
+        <v>7001035</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,32 +782,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133208875</v>
+        <v>133208877</v>
       </c>
       <c r="B3" t="n">
-        <v>92217</v>
+        <v>91881</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>658</v>
+        <v>5447</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>633908</v>
+        <v>633915</v>
       </c>
       <c r="R3" t="n">
-        <v>7001035</v>
+        <v>7000976</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -996,7 +996,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133208876</v>
+        <v>133208871</v>
       </c>
       <c r="B5" t="n">
         <v>91918</v>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>633874</v>
+        <v>633910</v>
       </c>
       <c r="R5" t="n">
-        <v>7001016</v>
+        <v>7001064</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,7 +1103,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133208871</v>
+        <v>133208876</v>
       </c>
       <c r="B6" t="n">
         <v>91918</v>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>633910</v>
+        <v>633874</v>
       </c>
       <c r="R6" t="n">
-        <v>7001064</v>
+        <v>7001016</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1183,7 +1183,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1651,42 +1651,46 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>133211039</v>
+        <v>133211048</v>
       </c>
       <c r="B11" t="n">
-        <v>57958</v>
+        <v>99130</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1694,13 +1698,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>633901</v>
+        <v>633875</v>
       </c>
       <c r="R11" t="n">
-        <v>7001035</v>
+        <v>7000940</v>
       </c>
       <c r="S11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1729,7 +1733,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1739,12 +1743,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:20</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1753,6 +1752,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1771,46 +1771,42 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>133211048</v>
+        <v>133211039</v>
       </c>
       <c r="B12" t="n">
-        <v>99130</v>
+        <v>57958</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1818,13 +1814,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>633875</v>
+        <v>633901</v>
       </c>
       <c r="R12" t="n">
-        <v>7000940</v>
+        <v>7001035</v>
       </c>
       <c r="S12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1853,7 +1849,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1863,7 +1859,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1872,7 +1873,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -2105,32 +2105,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133211042</v>
+        <v>133211052</v>
       </c>
       <c r="B15" t="n">
-        <v>91918</v>
+        <v>91881</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2140,10 +2140,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>633917</v>
+        <v>633829</v>
       </c>
       <c r="R15" t="n">
-        <v>7001045</v>
+        <v>7000951</v>
       </c>
       <c r="S15" t="n">
         <v>3</v>
@@ -2175,7 +2175,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>17:24</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2185,7 +2185,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>17:24</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2212,32 +2212,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>133211052</v>
+        <v>133211042</v>
       </c>
       <c r="B16" t="n">
-        <v>91881</v>
+        <v>91918</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2247,10 +2247,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>633829</v>
+        <v>633917</v>
       </c>
       <c r="R16" t="n">
-        <v>7000951</v>
+        <v>7001045</v>
       </c>
       <c r="S16" t="n">
         <v>3</v>
@@ -2282,7 +2282,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>17:24</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2292,7 +2292,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>17:24</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2974,37 +2974,42 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>133211037</v>
+        <v>133211046</v>
       </c>
       <c r="B23" t="n">
-        <v>92378</v>
+        <v>57958</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3012,10 +3017,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>633906</v>
+        <v>633920</v>
       </c>
       <c r="R23" t="n">
-        <v>7001068</v>
+        <v>7000986</v>
       </c>
       <c r="S23" t="n">
         <v>3</v>
@@ -3047,7 +3052,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3057,7 +3062,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>15:54</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3066,7 +3076,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3078,49 +3087,44 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>133211046</v>
+        <v>133211037</v>
       </c>
       <c r="B24" t="n">
-        <v>57958</v>
+        <v>92378</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3128,10 +3132,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>633920</v>
+        <v>633906</v>
       </c>
       <c r="R24" t="n">
-        <v>7000986</v>
+        <v>7001068</v>
       </c>
       <c r="S24" t="n">
         <v>3</v>
@@ -3163,7 +3167,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3173,12 +3177,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:54</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack på tall</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3187,6 +3186,7 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3198,7 +3198,7 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Markus Borja, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>

--- a/artfynd/A 16644-2026 artfynd.xlsx
+++ b/artfynd/A 16644-2026 artfynd.xlsx
@@ -1651,46 +1651,42 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>133211048</v>
+        <v>133211039</v>
       </c>
       <c r="B11" t="n">
-        <v>99130</v>
+        <v>57958</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1698,13 +1694,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>633875</v>
+        <v>633901</v>
       </c>
       <c r="R11" t="n">
-        <v>7000940</v>
+        <v>7001035</v>
       </c>
       <c r="S11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1733,7 +1729,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1743,7 +1739,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1752,7 +1753,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1771,42 +1771,46 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>133211039</v>
+        <v>133211048</v>
       </c>
       <c r="B12" t="n">
-        <v>57958</v>
+        <v>99130</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1814,13 +1818,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>633901</v>
+        <v>633875</v>
       </c>
       <c r="R12" t="n">
-        <v>7001035</v>
+        <v>7000940</v>
       </c>
       <c r="S12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1849,7 +1853,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1859,12 +1863,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:20</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1873,6 +1872,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 16644-2026 artfynd.xlsx
+++ b/artfynd/A 16644-2026 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133208875</v>
+        <v>133208877</v>
       </c>
       <c r="B2" t="n">
-        <v>92217</v>
+        <v>91881</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>658</v>
+        <v>5447</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>633908</v>
+        <v>633915</v>
       </c>
       <c r="R2" t="n">
-        <v>7001035</v>
+        <v>7000976</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,32 +782,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133208877</v>
+        <v>133208875</v>
       </c>
       <c r="B3" t="n">
-        <v>91881</v>
+        <v>92217</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5447</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>633915</v>
+        <v>633908</v>
       </c>
       <c r="R3" t="n">
-        <v>7000976</v>
+        <v>7001035</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1210,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133208874</v>
+        <v>133208872</v>
       </c>
       <c r="B7" t="n">
-        <v>92217</v>
+        <v>79333</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1221,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>633914</v>
+        <v>633893</v>
       </c>
       <c r="R7" t="n">
-        <v>7001038</v>
+        <v>7001068</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1280,7 +1280,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1290,7 +1290,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1317,10 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133208872</v>
+        <v>133208874</v>
       </c>
       <c r="B8" t="n">
-        <v>79333</v>
+        <v>92217</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1328,21 +1328,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1352,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>633893</v>
+        <v>633914</v>
       </c>
       <c r="R8" t="n">
-        <v>7001068</v>
+        <v>7001038</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1397,7 +1397,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1651,42 +1651,46 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>133211039</v>
+        <v>133211048</v>
       </c>
       <c r="B11" t="n">
-        <v>57958</v>
+        <v>99130</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1694,13 +1698,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>633901</v>
+        <v>633875</v>
       </c>
       <c r="R11" t="n">
-        <v>7001035</v>
+        <v>7000940</v>
       </c>
       <c r="S11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1729,7 +1733,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1739,12 +1743,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:20</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1753,6 +1752,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1771,46 +1771,42 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>133211048</v>
+        <v>133211039</v>
       </c>
       <c r="B12" t="n">
-        <v>99130</v>
+        <v>57958</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1818,13 +1814,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>633875</v>
+        <v>633901</v>
       </c>
       <c r="R12" t="n">
-        <v>7000940</v>
+        <v>7001035</v>
       </c>
       <c r="S12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1853,7 +1849,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1863,7 +1859,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1872,7 +1873,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -2105,32 +2105,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133211052</v>
+        <v>133211042</v>
       </c>
       <c r="B15" t="n">
-        <v>91881</v>
+        <v>91918</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2140,10 +2140,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>633829</v>
+        <v>633917</v>
       </c>
       <c r="R15" t="n">
-        <v>7000951</v>
+        <v>7001045</v>
       </c>
       <c r="S15" t="n">
         <v>3</v>
@@ -2175,7 +2175,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>17:24</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2185,7 +2185,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>17:24</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2212,32 +2212,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>133211042</v>
+        <v>133211052</v>
       </c>
       <c r="B16" t="n">
-        <v>91918</v>
+        <v>91881</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2247,10 +2247,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>633917</v>
+        <v>633829</v>
       </c>
       <c r="R16" t="n">
-        <v>7001045</v>
+        <v>7000951</v>
       </c>
       <c r="S16" t="n">
         <v>3</v>
@@ -2282,7 +2282,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>17:24</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2292,7 +2292,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>17:24</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2760,10 +2760,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>133211035</v>
+        <v>133211034</v>
       </c>
       <c r="B21" t="n">
-        <v>79333</v>
+        <v>91918</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2771,21 +2771,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2795,10 +2795,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>633904</v>
+        <v>633915</v>
       </c>
       <c r="R21" t="n">
-        <v>7001077</v>
+        <v>7001088</v>
       </c>
       <c r="S21" t="n">
         <v>3</v>
@@ -2830,7 +2830,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2840,7 +2840,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2867,10 +2867,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>133211034</v>
+        <v>133211035</v>
       </c>
       <c r="B22" t="n">
-        <v>91918</v>
+        <v>79333</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2878,21 +2878,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2902,10 +2902,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>633915</v>
+        <v>633904</v>
       </c>
       <c r="R22" t="n">
-        <v>7001088</v>
+        <v>7001077</v>
       </c>
       <c r="S22" t="n">
         <v>3</v>
@@ -2937,7 +2937,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2947,7 +2947,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2974,42 +2974,37 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>133211046</v>
+        <v>133211037</v>
       </c>
       <c r="B23" t="n">
-        <v>57958</v>
+        <v>92378</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3017,10 +3012,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>633920</v>
+        <v>633906</v>
       </c>
       <c r="R23" t="n">
-        <v>7000986</v>
+        <v>7001068</v>
       </c>
       <c r="S23" t="n">
         <v>3</v>
@@ -3052,7 +3047,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3062,12 +3057,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:54</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack på tall</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3076,6 +3066,7 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3087,44 +3078,49 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Markus Borja, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>133211037</v>
+        <v>133211046</v>
       </c>
       <c r="B24" t="n">
-        <v>92378</v>
+        <v>57958</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3132,10 +3128,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>633906</v>
+        <v>633920</v>
       </c>
       <c r="R24" t="n">
-        <v>7001068</v>
+        <v>7000986</v>
       </c>
       <c r="S24" t="n">
         <v>3</v>
@@ -3167,7 +3163,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3177,7 +3173,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>15:54</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3186,7 +3187,6 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3198,7 +3198,7 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>

--- a/artfynd/A 16644-2026 artfynd.xlsx
+++ b/artfynd/A 16644-2026 artfynd.xlsx
@@ -1651,42 +1651,46 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>133211039</v>
+        <v>133211048</v>
       </c>
       <c r="B11" t="n">
-        <v>57958</v>
+        <v>99130</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1694,13 +1698,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>633901</v>
+        <v>633875</v>
       </c>
       <c r="R11" t="n">
-        <v>7001035</v>
+        <v>7000940</v>
       </c>
       <c r="S11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1729,7 +1733,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1739,12 +1743,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:20</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1753,6 +1752,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1771,46 +1771,42 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>133211048</v>
+        <v>133211039</v>
       </c>
       <c r="B12" t="n">
-        <v>99130</v>
+        <v>57958</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1818,13 +1814,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>633875</v>
+        <v>633901</v>
       </c>
       <c r="R12" t="n">
-        <v>7000940</v>
+        <v>7001035</v>
       </c>
       <c r="S12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1853,7 +1849,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1863,7 +1859,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1872,7 +1873,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 16644-2026 artfynd.xlsx
+++ b/artfynd/A 16644-2026 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133208877</v>
+        <v>133208875</v>
       </c>
       <c r="B2" t="n">
-        <v>91881</v>
+        <v>92219</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5447</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>633915</v>
+        <v>633908</v>
       </c>
       <c r="R2" t="n">
-        <v>7000976</v>
+        <v>7001035</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,32 +782,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133208875</v>
+        <v>133208877</v>
       </c>
       <c r="B3" t="n">
-        <v>92217</v>
+        <v>91883</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>658</v>
+        <v>5447</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>633908</v>
+        <v>633915</v>
       </c>
       <c r="R3" t="n">
-        <v>7001035</v>
+        <v>7000976</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,7 +892,7 @@
         <v>133208873</v>
       </c>
       <c r="B4" t="n">
-        <v>79333</v>
+        <v>79334</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>133208871</v>
       </c>
       <c r="B5" t="n">
-        <v>91918</v>
+        <v>91920</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>133208876</v>
       </c>
       <c r="B6" t="n">
-        <v>91918</v>
+        <v>91920</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1210,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133208872</v>
+        <v>133208874</v>
       </c>
       <c r="B7" t="n">
-        <v>79333</v>
+        <v>92219</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1221,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>633893</v>
+        <v>633914</v>
       </c>
       <c r="R7" t="n">
-        <v>7001068</v>
+        <v>7001038</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1280,7 +1280,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1290,7 +1290,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1317,10 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133208874</v>
+        <v>133208872</v>
       </c>
       <c r="B8" t="n">
-        <v>92217</v>
+        <v>79334</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1328,21 +1328,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1352,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>633914</v>
+        <v>633893</v>
       </c>
       <c r="R8" t="n">
-        <v>7001038</v>
+        <v>7001068</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1397,7 +1397,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1427,7 +1427,7 @@
         <v>133211040</v>
       </c>
       <c r="B9" t="n">
-        <v>92217</v>
+        <v>92219</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1534,7 +1534,7 @@
         <v>133211051</v>
       </c>
       <c r="B10" t="n">
-        <v>99130</v>
+        <v>99132</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1774,7 +1774,7 @@
         <v>133211048</v>
       </c>
       <c r="B12" t="n">
-        <v>99130</v>
+        <v>99132</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1894,7 +1894,7 @@
         <v>133211036</v>
       </c>
       <c r="B13" t="n">
-        <v>91918</v>
+        <v>91920</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2001,7 +2001,7 @@
         <v>133211033</v>
       </c>
       <c r="B14" t="n">
-        <v>97995</v>
+        <v>97997</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2108,7 +2108,7 @@
         <v>133211042</v>
       </c>
       <c r="B15" t="n">
-        <v>91918</v>
+        <v>91920</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2215,7 +2215,7 @@
         <v>133211052</v>
       </c>
       <c r="B16" t="n">
-        <v>91881</v>
+        <v>91883</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2322,7 +2322,7 @@
         <v>133211050</v>
       </c>
       <c r="B17" t="n">
-        <v>91918</v>
+        <v>91920</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2429,7 +2429,7 @@
         <v>133211038</v>
       </c>
       <c r="B18" t="n">
-        <v>91918</v>
+        <v>91920</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2536,7 +2536,7 @@
         <v>133211045</v>
       </c>
       <c r="B19" t="n">
-        <v>79333</v>
+        <v>79334</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2760,10 +2760,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>133211034</v>
+        <v>133211035</v>
       </c>
       <c r="B21" t="n">
-        <v>91918</v>
+        <v>79334</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2771,21 +2771,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2795,10 +2795,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>633915</v>
+        <v>633904</v>
       </c>
       <c r="R21" t="n">
-        <v>7001088</v>
+        <v>7001077</v>
       </c>
       <c r="S21" t="n">
         <v>3</v>
@@ -2830,7 +2830,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2840,7 +2840,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2867,10 +2867,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>133211035</v>
+        <v>133211034</v>
       </c>
       <c r="B22" t="n">
-        <v>79333</v>
+        <v>91920</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2878,21 +2878,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2902,10 +2902,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>633904</v>
+        <v>633915</v>
       </c>
       <c r="R22" t="n">
-        <v>7001077</v>
+        <v>7001088</v>
       </c>
       <c r="S22" t="n">
         <v>3</v>
@@ -2937,7 +2937,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2947,7 +2947,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2977,7 +2977,7 @@
         <v>133211037</v>
       </c>
       <c r="B23" t="n">
-        <v>92378</v>
+        <v>92380</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 16644-2026 artfynd.xlsx
+++ b/artfynd/A 16644-2026 artfynd.xlsx
@@ -2760,10 +2760,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>133211035</v>
+        <v>133211034</v>
       </c>
       <c r="B21" t="n">
-        <v>79334</v>
+        <v>91920</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2771,21 +2771,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2795,10 +2795,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>633904</v>
+        <v>633915</v>
       </c>
       <c r="R21" t="n">
-        <v>7001077</v>
+        <v>7001088</v>
       </c>
       <c r="S21" t="n">
         <v>3</v>
@@ -2830,7 +2830,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2840,7 +2840,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2867,10 +2867,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>133211034</v>
+        <v>133211035</v>
       </c>
       <c r="B22" t="n">
-        <v>91920</v>
+        <v>79334</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2878,21 +2878,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2902,10 +2902,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>633915</v>
+        <v>633904</v>
       </c>
       <c r="R22" t="n">
-        <v>7001088</v>
+        <v>7001077</v>
       </c>
       <c r="S22" t="n">
         <v>3</v>
@@ -2937,7 +2937,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2947,7 +2947,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD22" t="b">

--- a/artfynd/A 16644-2026 artfynd.xlsx
+++ b/artfynd/A 16644-2026 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133208875</v>
+        <v>133208877</v>
       </c>
       <c r="B2" t="n">
-        <v>92219</v>
+        <v>91891</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>658</v>
+        <v>5447</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>633908</v>
+        <v>633915</v>
       </c>
       <c r="R2" t="n">
-        <v>7001035</v>
+        <v>7000976</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,32 +782,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133208877</v>
+        <v>133208875</v>
       </c>
       <c r="B3" t="n">
-        <v>91883</v>
+        <v>92227</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5447</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>633915</v>
+        <v>633908</v>
       </c>
       <c r="R3" t="n">
-        <v>7000976</v>
+        <v>7001035</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -999,7 +999,7 @@
         <v>133208871</v>
       </c>
       <c r="B5" t="n">
-        <v>91920</v>
+        <v>91928</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>133208876</v>
       </c>
       <c r="B6" t="n">
-        <v>91920</v>
+        <v>91928</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1210,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133208874</v>
+        <v>133208872</v>
       </c>
       <c r="B7" t="n">
-        <v>92219</v>
+        <v>79334</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1221,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>633914</v>
+        <v>633893</v>
       </c>
       <c r="R7" t="n">
-        <v>7001038</v>
+        <v>7001068</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1280,7 +1280,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1290,7 +1290,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1317,10 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133208872</v>
+        <v>133208874</v>
       </c>
       <c r="B8" t="n">
-        <v>79334</v>
+        <v>92227</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1328,21 +1328,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1352,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>633893</v>
+        <v>633914</v>
       </c>
       <c r="R8" t="n">
-        <v>7001068</v>
+        <v>7001038</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1397,7 +1397,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1427,7 +1427,7 @@
         <v>133211040</v>
       </c>
       <c r="B9" t="n">
-        <v>92219</v>
+        <v>92227</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1534,7 +1534,7 @@
         <v>133211051</v>
       </c>
       <c r="B10" t="n">
-        <v>99132</v>
+        <v>99140</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1774,7 +1774,7 @@
         <v>133211048</v>
       </c>
       <c r="B12" t="n">
-        <v>99132</v>
+        <v>99140</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1894,7 +1894,7 @@
         <v>133211036</v>
       </c>
       <c r="B13" t="n">
-        <v>91920</v>
+        <v>91928</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2001,7 +2001,7 @@
         <v>133211033</v>
       </c>
       <c r="B14" t="n">
-        <v>97997</v>
+        <v>98005</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2108,7 +2108,7 @@
         <v>133211042</v>
       </c>
       <c r="B15" t="n">
-        <v>91920</v>
+        <v>91928</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2215,7 +2215,7 @@
         <v>133211052</v>
       </c>
       <c r="B16" t="n">
-        <v>91883</v>
+        <v>91891</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2322,7 +2322,7 @@
         <v>133211050</v>
       </c>
       <c r="B17" t="n">
-        <v>91920</v>
+        <v>91928</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2429,7 +2429,7 @@
         <v>133211038</v>
       </c>
       <c r="B18" t="n">
-        <v>91920</v>
+        <v>91928</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2760,10 +2760,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>133211034</v>
+        <v>133211035</v>
       </c>
       <c r="B21" t="n">
-        <v>91920</v>
+        <v>79334</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2771,21 +2771,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2795,10 +2795,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>633915</v>
+        <v>633904</v>
       </c>
       <c r="R21" t="n">
-        <v>7001088</v>
+        <v>7001077</v>
       </c>
       <c r="S21" t="n">
         <v>3</v>
@@ -2830,7 +2830,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2840,7 +2840,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2867,10 +2867,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>133211035</v>
+        <v>133211034</v>
       </c>
       <c r="B22" t="n">
-        <v>79334</v>
+        <v>91928</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2878,21 +2878,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2902,10 +2902,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>633904</v>
+        <v>633915</v>
       </c>
       <c r="R22" t="n">
-        <v>7001077</v>
+        <v>7001088</v>
       </c>
       <c r="S22" t="n">
         <v>3</v>
@@ -2937,7 +2937,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2947,7 +2947,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2977,7 +2977,7 @@
         <v>133211037</v>
       </c>
       <c r="B23" t="n">
-        <v>92380</v>
+        <v>92388</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 16644-2026 artfynd.xlsx
+++ b/artfynd/A 16644-2026 artfynd.xlsx
@@ -2760,10 +2760,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>133211035</v>
+        <v>133211034</v>
       </c>
       <c r="B21" t="n">
-        <v>79334</v>
+        <v>91928</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2771,21 +2771,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2795,10 +2795,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>633904</v>
+        <v>633915</v>
       </c>
       <c r="R21" t="n">
-        <v>7001077</v>
+        <v>7001088</v>
       </c>
       <c r="S21" t="n">
         <v>3</v>
@@ -2830,7 +2830,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2840,7 +2840,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2867,10 +2867,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>133211034</v>
+        <v>133211035</v>
       </c>
       <c r="B22" t="n">
-        <v>91928</v>
+        <v>79334</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2878,21 +2878,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2902,10 +2902,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>633915</v>
+        <v>633904</v>
       </c>
       <c r="R22" t="n">
-        <v>7001088</v>
+        <v>7001077</v>
       </c>
       <c r="S22" t="n">
         <v>3</v>
@@ -2937,7 +2937,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2947,7 +2947,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD22" t="b">

--- a/artfynd/A 16644-2026 artfynd.xlsx
+++ b/artfynd/A 16644-2026 artfynd.xlsx
@@ -2760,10 +2760,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>133211034</v>
+        <v>133211035</v>
       </c>
       <c r="B21" t="n">
-        <v>91928</v>
+        <v>79334</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2771,21 +2771,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2795,10 +2795,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>633915</v>
+        <v>633904</v>
       </c>
       <c r="R21" t="n">
-        <v>7001088</v>
+        <v>7001077</v>
       </c>
       <c r="S21" t="n">
         <v>3</v>
@@ -2830,7 +2830,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2840,7 +2840,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2867,10 +2867,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>133211035</v>
+        <v>133211034</v>
       </c>
       <c r="B22" t="n">
-        <v>79334</v>
+        <v>91928</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2878,21 +2878,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2902,10 +2902,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>633904</v>
+        <v>633915</v>
       </c>
       <c r="R22" t="n">
-        <v>7001077</v>
+        <v>7001088</v>
       </c>
       <c r="S22" t="n">
         <v>3</v>
@@ -2937,7 +2937,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2947,7 +2947,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD22" t="b">

--- a/artfynd/A 16644-2026 artfynd.xlsx
+++ b/artfynd/A 16644-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133208877</v>
       </c>
       <c r="B2" t="n">
-        <v>91891</v>
+        <v>91910</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>133208875</v>
       </c>
       <c r="B3" t="n">
-        <v>92227</v>
+        <v>92218</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>133208873</v>
       </c>
       <c r="B4" t="n">
-        <v>79334</v>
+        <v>79348</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133208871</v>
+        <v>133208876</v>
       </c>
       <c r="B5" t="n">
-        <v>91928</v>
+        <v>91947</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>633910</v>
+        <v>633874</v>
       </c>
       <c r="R5" t="n">
-        <v>7001064</v>
+        <v>7001016</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133208876</v>
+        <v>133208871</v>
       </c>
       <c r="B6" t="n">
-        <v>91928</v>
+        <v>91947</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>633874</v>
+        <v>633910</v>
       </c>
       <c r="R6" t="n">
-        <v>7001016</v>
+        <v>7001064</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1183,7 +1183,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133208872</v>
+        <v>133208874</v>
       </c>
       <c r="B7" t="n">
-        <v>79334</v>
+        <v>92218</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1221,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>633893</v>
+        <v>633914</v>
       </c>
       <c r="R7" t="n">
-        <v>7001068</v>
+        <v>7001038</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1280,7 +1280,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1290,7 +1290,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1317,10 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133208874</v>
+        <v>133208872</v>
       </c>
       <c r="B8" t="n">
-        <v>92227</v>
+        <v>79348</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1328,21 +1328,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1352,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>633914</v>
+        <v>633893</v>
       </c>
       <c r="R8" t="n">
-        <v>7001038</v>
+        <v>7001068</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1397,7 +1397,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1427,7 +1427,7 @@
         <v>133211040</v>
       </c>
       <c r="B9" t="n">
-        <v>92227</v>
+        <v>92218</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1534,7 +1534,7 @@
         <v>133211051</v>
       </c>
       <c r="B10" t="n">
-        <v>99140</v>
+        <v>99168</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1654,7 +1654,7 @@
         <v>133211039</v>
       </c>
       <c r="B11" t="n">
-        <v>57958</v>
+        <v>57965</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1774,7 +1774,7 @@
         <v>133211048</v>
       </c>
       <c r="B12" t="n">
-        <v>99140</v>
+        <v>99168</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1894,7 +1894,7 @@
         <v>133211036</v>
       </c>
       <c r="B13" t="n">
-        <v>91928</v>
+        <v>91947</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2001,7 +2001,7 @@
         <v>133211033</v>
       </c>
       <c r="B14" t="n">
-        <v>98005</v>
+        <v>98033</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2105,32 +2105,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133211042</v>
+        <v>133211052</v>
       </c>
       <c r="B15" t="n">
-        <v>91928</v>
+        <v>91910</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2140,10 +2140,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>633917</v>
+        <v>633829</v>
       </c>
       <c r="R15" t="n">
-        <v>7001045</v>
+        <v>7000951</v>
       </c>
       <c r="S15" t="n">
         <v>3</v>
@@ -2175,7 +2175,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>17:24</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2185,7 +2185,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>17:24</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2212,32 +2212,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>133211052</v>
+        <v>133211042</v>
       </c>
       <c r="B16" t="n">
-        <v>91891</v>
+        <v>91947</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2247,10 +2247,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>633829</v>
+        <v>633917</v>
       </c>
       <c r="R16" t="n">
-        <v>7000951</v>
+        <v>7001045</v>
       </c>
       <c r="S16" t="n">
         <v>3</v>
@@ -2282,7 +2282,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>17:24</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2292,7 +2292,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>17:24</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2322,7 +2322,7 @@
         <v>133211050</v>
       </c>
       <c r="B17" t="n">
-        <v>91928</v>
+        <v>91947</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2429,7 +2429,7 @@
         <v>133211038</v>
       </c>
       <c r="B18" t="n">
-        <v>91928</v>
+        <v>91947</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2536,7 +2536,7 @@
         <v>133211045</v>
       </c>
       <c r="B19" t="n">
-        <v>79334</v>
+        <v>79348</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2643,7 +2643,7 @@
         <v>133211044</v>
       </c>
       <c r="B20" t="n">
-        <v>57958</v>
+        <v>57965</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2763,7 +2763,7 @@
         <v>133211034</v>
       </c>
       <c r="B21" t="n">
-        <v>91928</v>
+        <v>91947</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2870,7 +2870,7 @@
         <v>133211035</v>
       </c>
       <c r="B22" t="n">
-        <v>79334</v>
+        <v>79348</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2974,37 +2974,42 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>133211037</v>
+        <v>133211046</v>
       </c>
       <c r="B23" t="n">
-        <v>92388</v>
+        <v>57965</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3012,10 +3017,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>633906</v>
+        <v>633920</v>
       </c>
       <c r="R23" t="n">
-        <v>7001068</v>
+        <v>7000986</v>
       </c>
       <c r="S23" t="n">
         <v>3</v>
@@ -3047,7 +3052,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3057,7 +3062,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>15:54</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3066,7 +3076,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3078,49 +3087,44 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>133211046</v>
+        <v>133211037</v>
       </c>
       <c r="B24" t="n">
-        <v>57958</v>
+        <v>92379</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3128,10 +3132,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>633920</v>
+        <v>633906</v>
       </c>
       <c r="R24" t="n">
-        <v>7000986</v>
+        <v>7001068</v>
       </c>
       <c r="S24" t="n">
         <v>3</v>
@@ -3163,7 +3167,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3173,12 +3177,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:54</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack på tall</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3187,6 +3186,7 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3198,7 +3198,7 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Markus Borja, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>

--- a/artfynd/A 16644-2026 artfynd.xlsx
+++ b/artfynd/A 16644-2026 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133208877</v>
+        <v>133208875</v>
       </c>
       <c r="B2" t="n">
-        <v>91910</v>
+        <v>92218</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5447</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>633915</v>
+        <v>633908</v>
       </c>
       <c r="R2" t="n">
-        <v>7000976</v>
+        <v>7001035</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,32 +782,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133208875</v>
+        <v>133208877</v>
       </c>
       <c r="B3" t="n">
-        <v>92218</v>
+        <v>91910</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>658</v>
+        <v>5447</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>633908</v>
+        <v>633915</v>
       </c>
       <c r="R3" t="n">
-        <v>7001035</v>
+        <v>7000976</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -996,7 +996,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133208876</v>
+        <v>133208871</v>
       </c>
       <c r="B5" t="n">
         <v>91947</v>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>633874</v>
+        <v>633910</v>
       </c>
       <c r="R5" t="n">
-        <v>7001016</v>
+        <v>7001064</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,7 +1103,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133208871</v>
+        <v>133208876</v>
       </c>
       <c r="B6" t="n">
         <v>91947</v>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>633910</v>
+        <v>633874</v>
       </c>
       <c r="R6" t="n">
-        <v>7001064</v>
+        <v>7001016</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1183,7 +1183,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -2760,10 +2760,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>133211034</v>
+        <v>133211035</v>
       </c>
       <c r="B21" t="n">
-        <v>91947</v>
+        <v>79348</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2771,21 +2771,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2795,10 +2795,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>633915</v>
+        <v>633904</v>
       </c>
       <c r="R21" t="n">
-        <v>7001088</v>
+        <v>7001077</v>
       </c>
       <c r="S21" t="n">
         <v>3</v>
@@ -2830,7 +2830,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2840,7 +2840,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2867,10 +2867,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>133211035</v>
+        <v>133211034</v>
       </c>
       <c r="B22" t="n">
-        <v>79348</v>
+        <v>91947</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2878,21 +2878,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2902,10 +2902,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>633904</v>
+        <v>633915</v>
       </c>
       <c r="R22" t="n">
-        <v>7001077</v>
+        <v>7001088</v>
       </c>
       <c r="S22" t="n">
         <v>3</v>
@@ -2937,7 +2937,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2947,7 +2947,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD22" t="b">

--- a/artfynd/A 16644-2026 artfynd.xlsx
+++ b/artfynd/A 16644-2026 artfynd.xlsx
@@ -1427,7 +1427,7 @@
         <v>133211040</v>
       </c>
       <c r="B9" t="n">
-        <v>92218</v>
+        <v>92228</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1534,7 +1534,7 @@
         <v>133211051</v>
       </c>
       <c r="B10" t="n">
-        <v>99168</v>
+        <v>99178</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1654,7 +1654,7 @@
         <v>133211039</v>
       </c>
       <c r="B11" t="n">
-        <v>57965</v>
+        <v>57975</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1774,7 +1774,7 @@
         <v>133211048</v>
       </c>
       <c r="B12" t="n">
-        <v>99168</v>
+        <v>99178</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1894,7 +1894,7 @@
         <v>133211036</v>
       </c>
       <c r="B13" t="n">
-        <v>91947</v>
+        <v>91957</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2001,7 +2001,7 @@
         <v>133211033</v>
       </c>
       <c r="B14" t="n">
-        <v>98033</v>
+        <v>98043</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2108,7 +2108,7 @@
         <v>133211052</v>
       </c>
       <c r="B15" t="n">
-        <v>91910</v>
+        <v>91920</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2215,7 +2215,7 @@
         <v>133211042</v>
       </c>
       <c r="B16" t="n">
-        <v>91947</v>
+        <v>91957</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2322,7 +2322,7 @@
         <v>133211050</v>
       </c>
       <c r="B17" t="n">
-        <v>91947</v>
+        <v>91957</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2429,7 +2429,7 @@
         <v>133211038</v>
       </c>
       <c r="B18" t="n">
-        <v>91947</v>
+        <v>91957</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2536,7 +2536,7 @@
         <v>133211045</v>
       </c>
       <c r="B19" t="n">
-        <v>79348</v>
+        <v>79358</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2643,7 +2643,7 @@
         <v>133211044</v>
       </c>
       <c r="B20" t="n">
-        <v>57965</v>
+        <v>57975</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2763,7 +2763,7 @@
         <v>133211035</v>
       </c>
       <c r="B21" t="n">
-        <v>79348</v>
+        <v>79358</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2870,7 +2870,7 @@
         <v>133211034</v>
       </c>
       <c r="B22" t="n">
-        <v>91947</v>
+        <v>91957</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2974,42 +2974,37 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>133211046</v>
+        <v>133211037</v>
       </c>
       <c r="B23" t="n">
-        <v>57965</v>
+        <v>92389</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3017,10 +3012,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>633920</v>
+        <v>633906</v>
       </c>
       <c r="R23" t="n">
-        <v>7000986</v>
+        <v>7001068</v>
       </c>
       <c r="S23" t="n">
         <v>3</v>
@@ -3052,7 +3047,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3062,12 +3057,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:54</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack på tall</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3076,6 +3066,7 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3087,44 +3078,49 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Markus Borja, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>133211037</v>
+        <v>133211046</v>
       </c>
       <c r="B24" t="n">
-        <v>92379</v>
+        <v>57975</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3132,10 +3128,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>633906</v>
+        <v>633920</v>
       </c>
       <c r="R24" t="n">
-        <v>7001068</v>
+        <v>7000986</v>
       </c>
       <c r="S24" t="n">
         <v>3</v>
@@ -3167,7 +3163,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3177,7 +3173,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>15:54</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3186,7 +3187,6 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3198,7 +3198,7 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
